--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487063_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487063_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>10.262</v>
+        <v>10.0052</v>
       </c>
       <c r="E2" t="n">
-        <v>9.0495</v>
+        <v>8.6053</v>
       </c>
       <c r="F2" t="n">
-        <v>1.2126</v>
+        <v>1.3999</v>
       </c>
       <c r="G2" t="n">
         <v>7.0859</v>
@@ -610,13 +610,13 @@
         <v>2.5091</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.7357</v>
+        <v>-0.9925</v>
       </c>
       <c r="T2" t="n">
-        <v>0.5897</v>
+        <v>0.1455</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.3253</v>
+        <v>-1.138</v>
       </c>
       <c r="V2" t="n">
         <v>4.2979</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.4982</v>
+        <v>7.4629</v>
       </c>
       <c r="E3" t="n">
-        <v>4.6925</v>
+        <v>5.7911</v>
       </c>
       <c r="F3" t="n">
-        <v>1.8057</v>
+        <v>1.6718</v>
       </c>
       <c r="G3" t="n">
         <v>3.7439</v>
@@ -688,13 +688,13 @@
         <v>2.5091</v>
       </c>
       <c r="S3" t="n">
-        <v>-2.3432</v>
+        <v>-1.3785</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.5321</v>
+        <v>-0.4336</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.8111</v>
+        <v>-0.9449</v>
       </c>
       <c r="V3" t="n">
         <v>5.4836</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.7941</v>
+        <v>3.9666</v>
       </c>
       <c r="E4" t="n">
-        <v>2.9563</v>
+        <v>2.5934</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8377</v>
+        <v>1.3731</v>
       </c>
       <c r="G4" t="n">
         <v>2.3181</v>
@@ -766,13 +766,13 @@
         <v>2.1231</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.07530000000000001</v>
+        <v>0.09719999999999999</v>
       </c>
       <c r="T4" t="n">
-        <v>1.0061</v>
+        <v>0.6432</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.0814</v>
+        <v>-0.546</v>
       </c>
       <c r="V4" t="n">
         <v>-0.5717</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.4515</v>
+        <v>3.3732</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2275</v>
+        <v>0.9255</v>
       </c>
       <c r="F5" t="n">
-        <v>3.2241</v>
+        <v>2.4478</v>
       </c>
       <c r="G5" t="n">
         <v>3.2122</v>
@@ -844,13 +844,13 @@
         <v>1.9301</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1118</v>
+        <v>-0.1901</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.9967</v>
+        <v>-0.2987</v>
       </c>
       <c r="U5" t="n">
-        <v>0.885</v>
+        <v>0.1087</v>
       </c>
       <c r="V5" t="n">
         <v>-0.614</v>
@@ -877,10 +877,10 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3879</v>
+        <v>0.08749999999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3733</v>
+        <v>0.07290000000000001</v>
       </c>
       <c r="F6" t="n">
         <v>0.0147</v>
@@ -922,10 +922,10 @@
         <v>0.772</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2525</v>
+        <v>-0.5528999999999999</v>
       </c>
       <c r="T6" t="n">
-        <v>0.3847</v>
+        <v>0.0843</v>
       </c>
       <c r="U6" t="n">
         <v>-0.6372</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. AREVALO NEGUERUELA</t>
+          <t>D. IBARLUCEA LAVIN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.2667</v>
+        <v>0.003</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.1164</v>
+        <v>-0.4829</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.1503</v>
+        <v>0.4859</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2959</v>
+        <v>1.5664</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.0983</v>
+        <v>0.8209</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3941</v>
+        <v>0.7454</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0621</v>
+        <v>1.8458</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0621</v>
+        <v>1.1953</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>0.6505</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2338</v>
+        <v>-0.2795</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.1604</v>
+        <v>-0.3744</v>
       </c>
       <c r="O7" t="n">
-        <v>0.3941</v>
+        <v>0.0949</v>
       </c>
       <c r="P7" t="n">
-        <v>0.193</v>
+        <v>-0.772</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-2.8951</v>
       </c>
       <c r="R7" t="n">
-        <v>0.193</v>
+        <v>2.1231</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.7978</v>
+        <v>-0.5476</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1785</v>
+        <v>-0.0476</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.6194</v>
+        <v>-0.5001</v>
       </c>
       <c r="V7" t="n">
-        <v>0.0422</v>
+        <v>-0.2436</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.614</v>
       </c>
       <c r="X7" t="n">
-        <v>0.0422</v>
+        <v>-0.8576</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D. IBARLUCEA LAVIN</t>
+          <t>A. AREVALO NEGUERUELA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.5076000000000001</v>
+        <v>-0.2399</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.1809</v>
+        <v>-0.1164</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6733</v>
+        <v>-0.1236</v>
       </c>
       <c r="G8" t="n">
-        <v>1.5664</v>
+        <v>0.2959</v>
       </c>
       <c r="H8" t="n">
-        <v>0.8209</v>
+        <v>-0.0983</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7454</v>
+        <v>0.3941</v>
       </c>
       <c r="J8" t="n">
-        <v>1.8458</v>
+        <v>0.0621</v>
       </c>
       <c r="K8" t="n">
-        <v>1.1953</v>
+        <v>0.0621</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6505</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.2795</v>
+        <v>0.2338</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.3744</v>
+        <v>-0.1604</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0949</v>
+        <v>0.3941</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.772</v>
+        <v>0.193</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.8951</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.1231</v>
+        <v>0.193</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.0583</v>
+        <v>-0.7711</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.7456</v>
+        <v>-0.1785</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3127</v>
+        <v>-0.5926</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.2436</v>
+        <v>0.0422</v>
       </c>
       <c r="W8" t="n">
-        <v>0.614</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.8576</v>
+        <v>0.0422</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.0155</v>
+        <v>-2.4692</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.5643</v>
+        <v>-2.2857</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.4513</v>
+        <v>-0.1836</v>
       </c>
       <c r="G9" t="n">
         <v>-2.4365</v>
@@ -1156,13 +1156,13 @@
         <v>0.772</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.3511</v>
+        <v>-0.8048</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3278</v>
+        <v>-0.0492</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.0232</v>
+        <v>-0.7554999999999999</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.6615</v>
+        <v>-5.4622</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.8232</v>
+        <v>-4.7042</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.8384</v>
+        <v>-0.758</v>
       </c>
       <c r="G10" t="n">
         <v>-3.9403</v>
@@ -1234,13 +1234,13 @@
         <v>1.5441</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.7634</v>
+        <v>-0.5642</v>
       </c>
       <c r="T10" t="n">
-        <v>0.2208</v>
+        <v>0.3398</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.9842</v>
+        <v>-0.9039</v>
       </c>
       <c r="V10" t="n">
         <v>-0.5717</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>14.9424</v>
+        <v>16.7271</v>
       </c>
       <c r="E11" t="n">
-        <v>8.614300000000004</v>
+        <v>10.399</v>
       </c>
       <c r="F11" t="n">
-        <v>6.3281</v>
+        <v>6.328</v>
       </c>
       <c r="G11" t="n">
         <v>11.714</v>
@@ -1312,10 +1312,10 @@
         <v>14.4756</v>
       </c>
       <c r="S11" t="n">
-        <v>-7.4891</v>
+        <v>-5.704499999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.5794</v>
+        <v>0.2051999999999999</v>
       </c>
       <c r="U11" t="n">
         <v>-5.9095</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>4.8186</v>
+        <v>3.3301</v>
       </c>
       <c r="E12" t="n">
-        <v>4.996</v>
+        <v>3.2936</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.1774</v>
+        <v>0.0365</v>
       </c>
       <c r="G12" t="n">
         <v>1.2479</v>
@@ -1390,13 +1390,13 @@
         <v>1.7371</v>
       </c>
       <c r="S12" t="n">
-        <v>3.2567</v>
+        <v>1.7682</v>
       </c>
       <c r="T12" t="n">
-        <v>3.2746</v>
+        <v>1.5722</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0179</v>
+        <v>0.1959</v>
       </c>
       <c r="V12" t="n">
         <v>2.4371</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.7113</v>
+        <v>1.3823</v>
       </c>
       <c r="E13" t="n">
-        <v>2.3849</v>
+        <v>1.0831</v>
       </c>
       <c r="F13" t="n">
-        <v>0.3264</v>
+        <v>0.2993</v>
       </c>
       <c r="G13" t="n">
         <v>1.2265</v>
@@ -1468,13 +1468,13 @@
         <v>1.7371</v>
       </c>
       <c r="S13" t="n">
-        <v>2.7273</v>
+        <v>1.3983</v>
       </c>
       <c r="T13" t="n">
-        <v>2.1774</v>
+        <v>0.8754999999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>0.5499000000000001</v>
+        <v>0.5228</v>
       </c>
       <c r="V13" t="n">
         <v>-0.08450000000000001</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. GUTIEZ SALGADO</t>
+          <t>G. HUESO GUTIERREZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.7106</v>
+        <v>1.2422</v>
       </c>
       <c r="E14" t="n">
-        <v>0.0361</v>
+        <v>-0.06759999999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>0.6745</v>
+        <v>1.3098</v>
       </c>
       <c r="G14" t="n">
-        <v>-1.1648</v>
+        <v>1.1088</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.8174</v>
+        <v>0.3405</v>
       </c>
       <c r="I14" t="n">
-        <v>0.6526</v>
+        <v>0.7683</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.2574</v>
+        <v>0.6808999999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.1347</v>
+        <v>0.1604</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.1228</v>
+        <v>0.5205</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.9074</v>
+        <v>0.4279</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.6828</v>
+        <v>0.1801</v>
       </c>
       <c r="O14" t="n">
-        <v>0.7754</v>
+        <v>0.2478</v>
       </c>
       <c r="P14" t="n">
-        <v>0.772</v>
+        <v>0.579</v>
       </c>
       <c r="Q14" t="n">
         <v>-0.965</v>
       </c>
       <c r="R14" t="n">
-        <v>1.7371</v>
+        <v>1.5441</v>
       </c>
       <c r="S14" t="n">
-        <v>1.0378</v>
+        <v>0.7823</v>
       </c>
       <c r="T14" t="n">
-        <v>1.2586</v>
+        <v>0.2165</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.2208</v>
+        <v>0.5658</v>
       </c>
       <c r="V14" t="n">
-        <v>0.06560000000000001</v>
+        <v>-1.228</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>0.06560000000000001</v>
+        <v>-1.228</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>G. HUESO GUTIERREZ</t>
+          <t>A. GUTIEZ SALGADO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0738</v>
+        <v>0.7113</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.9689</v>
+        <v>-0.3645</v>
       </c>
       <c r="F15" t="n">
-        <v>1.0427</v>
+        <v>1.0757</v>
       </c>
       <c r="G15" t="n">
-        <v>1.1088</v>
+        <v>-1.1648</v>
       </c>
       <c r="H15" t="n">
-        <v>0.3405</v>
+        <v>-1.8174</v>
       </c>
       <c r="I15" t="n">
-        <v>0.7683</v>
+        <v>0.6526</v>
       </c>
       <c r="J15" t="n">
-        <v>0.6808999999999999</v>
+        <v>-0.2574</v>
       </c>
       <c r="K15" t="n">
-        <v>0.1604</v>
+        <v>-0.1347</v>
       </c>
       <c r="L15" t="n">
-        <v>0.5205</v>
+        <v>-0.1228</v>
       </c>
       <c r="M15" t="n">
-        <v>0.4279</v>
+        <v>-0.9074</v>
       </c>
       <c r="N15" t="n">
-        <v>0.1801</v>
+        <v>-1.6828</v>
       </c>
       <c r="O15" t="n">
-        <v>0.2478</v>
+        <v>0.7754</v>
       </c>
       <c r="P15" t="n">
-        <v>0.579</v>
+        <v>0.772</v>
       </c>
       <c r="Q15" t="n">
         <v>-0.965</v>
       </c>
       <c r="R15" t="n">
-        <v>1.5441</v>
+        <v>1.7371</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.386</v>
+        <v>1.0384</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.6848</v>
+        <v>0.858</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2987</v>
+        <v>0.1804</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.228</v>
+        <v>0.06560000000000001</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.228</v>
+        <v>0.06560000000000001</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.3802</v>
+        <v>0.4811</v>
       </c>
       <c r="E16" t="n">
-        <v>-2.375</v>
+        <v>-1.674</v>
       </c>
       <c r="F16" t="n">
-        <v>1.9948</v>
+        <v>2.1551</v>
       </c>
       <c r="G16" t="n">
         <v>-0.7119</v>
@@ -1702,13 +1702,13 @@
         <v>1.5441</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.0271</v>
+        <v>0.8342000000000001</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.2102</v>
+        <v>0.4908</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1831</v>
+        <v>0.3434</v>
       </c>
       <c r="V16" t="n">
         <v>-0.2202</v>
@@ -1735,10 +1735,10 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.6735</v>
+        <v>-0.5733</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.0595</v>
+        <v>0.0407</v>
       </c>
       <c r="F17" t="n">
         <v>-0.614</v>
@@ -1780,10 +1780,10 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.193</v>
+        <v>-0.0929</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.0595</v>
+        <v>0.0407</v>
       </c>
       <c r="U17" t="n">
         <v>-0.1335</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.1548</v>
+        <v>-1.9013</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.4377</v>
+        <v>-1.2374</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.717</v>
+        <v>-0.6637999999999999</v>
       </c>
       <c r="G18" t="n">
         <v>-1.9677</v>
@@ -1858,13 +1858,13 @@
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.1871</v>
+        <v>0.0664</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1639</v>
+        <v>0.0364</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0231</v>
+        <v>0.0301</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.0899</v>
+        <v>-2.9563</v>
       </c>
       <c r="E19" t="n">
         <v>-0.4887</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.6012</v>
+        <v>-2.4677</v>
       </c>
       <c r="G19" t="n">
         <v>-0.1346</v>
@@ -1936,13 +1936,13 @@
         <v>0.772</v>
       </c>
       <c r="S19" t="n">
-        <v>0.5936</v>
+        <v>0.7271</v>
       </c>
       <c r="T19" t="n">
         <v>0.3847</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2089</v>
+        <v>0.3424</v>
       </c>
       <c r="V19" t="n">
         <v>-3.3558</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>G. MARTINEZ DE OSABA ANTOLIN</t>
+          <t>P. ALBISU ASTIGARRAGA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-4.4747</v>
+        <v>-4.5067</v>
       </c>
       <c r="E20" t="n">
-        <v>0.111</v>
+        <v>-3.2012</v>
       </c>
       <c r="F20" t="n">
-        <v>-4.5857</v>
+        <v>-1.3055</v>
       </c>
       <c r="G20" t="n">
-        <v>-3.8966</v>
+        <v>-4.2951</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.425</v>
+        <v>-2.6329</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.4716</v>
+        <v>-1.6622</v>
       </c>
       <c r="J20" t="n">
-        <v>-2.0213</v>
+        <v>-2.0059</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.1813</v>
+        <v>-0.1087</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.84</v>
+        <v>-1.8971</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.8753</v>
+        <v>-2.2893</v>
       </c>
       <c r="N20" t="n">
-        <v>-2.2437</v>
+        <v>-2.5242</v>
       </c>
       <c r="O20" t="n">
-        <v>0.3684</v>
+        <v>0.2349</v>
       </c>
       <c r="P20" t="n">
-        <v>0.965</v>
+        <v>-0.579</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-1.9301</v>
       </c>
       <c r="R20" t="n">
-        <v>0.965</v>
+        <v>1.3511</v>
       </c>
       <c r="S20" t="n">
-        <v>1.1752</v>
+        <v>0.6299</v>
       </c>
       <c r="T20" t="n">
-        <v>0.9466</v>
+        <v>0.4489</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2287</v>
+        <v>0.1811</v>
       </c>
       <c r="V20" t="n">
-        <v>-2.7184</v>
+        <v>-0.2625</v>
       </c>
       <c r="W20" t="n">
-        <v>1.1857</v>
+        <v>0.2859</v>
       </c>
       <c r="X20" t="n">
-        <v>-3.9041</v>
+        <v>-0.5484</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>P. ALBISU ASTIGARRAGA</t>
+          <t>G. MARTINEZ DE OSABA ANTOLIN</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-5.294</v>
+        <v>-4.6486</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.2026</v>
+        <v>-0.0893</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.0913</v>
+        <v>-4.5593</v>
       </c>
       <c r="G21" t="n">
-        <v>-4.2951</v>
+        <v>-3.8966</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.6329</v>
+        <v>-2.425</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.6622</v>
+        <v>-1.4716</v>
       </c>
       <c r="J21" t="n">
-        <v>-2.0059</v>
+        <v>-2.0213</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.1087</v>
+        <v>-0.1813</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.8971</v>
+        <v>-1.84</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.2893</v>
+        <v>-1.8753</v>
       </c>
       <c r="N21" t="n">
-        <v>-2.5242</v>
+        <v>-2.2437</v>
       </c>
       <c r="O21" t="n">
-        <v>0.2349</v>
+        <v>0.3684</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.579</v>
+        <v>0.965</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.9301</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.3511</v>
+        <v>0.965</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1573</v>
+        <v>1.0014</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5525</v>
+        <v>0.7463</v>
       </c>
       <c r="U21" t="n">
-        <v>0.3952</v>
+        <v>0.2551</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.2625</v>
+        <v>-2.7184</v>
       </c>
       <c r="W21" t="n">
-        <v>0.2859</v>
+        <v>1.1857</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.5484</v>
+        <v>-3.9041</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-7.1899</v>
+        <v>-6.168</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.3236</v>
+        <v>-3.6226</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.8663</v>
+        <v>-2.5454</v>
       </c>
       <c r="G22" t="n">
         <v>-2.6459</v>
@@ -2170,13 +2170,13 @@
         <v>0.193</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.351</v>
+        <v>0.6709000000000001</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4614</v>
+        <v>0.2396</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1104</v>
+        <v>0.4313</v>
       </c>
       <c r="V22" t="n">
         <v>-2.4559</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-14.9427</v>
+        <v>-13.6072</v>
       </c>
       <c r="E23" t="n">
-        <v>-6.327999999999999</v>
+        <v>-6.327900000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>-8.6145</v>
+        <v>-7.2793</v>
       </c>
       <c r="G23" t="n">
         <v>-11.7139</v>
@@ -2248,13 +2248,13 @@
         <v>11.5806</v>
       </c>
       <c r="S23" t="n">
-        <v>7.4891</v>
+        <v>8.824199999999999</v>
       </c>
       <c r="T23" t="n">
         <v>5.9096</v>
       </c>
       <c r="U23" t="n">
-        <v>1.5796</v>
+        <v>2.9148</v>
       </c>
       <c r="V23" t="n">
         <v>-7.8226</v>
